--- a/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
@@ -76,7 +76,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">c8dc29a766acf8868fc9706a64afd79a56c4194d</t>
+          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
         </is>
       </c>
     </row>
@@ -88,7 +88,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 00:52:12</t>
+          <t xml:space="preserve">2026-08-27 01:07:32</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:46:59</t>
+          <t xml:space="preserve">2026-08-27 04:04:57</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">

--- a/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
@@ -76,7 +76,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
+          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
         </is>
       </c>
     </row>
@@ -88,7 +88,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:07:32</t>
+          <t xml:space="preserve">2026-08-27 01:16:52</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:04:57</t>
+          <t xml:space="preserve">2026-08-27 04:13:39</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">

--- a/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
@@ -76,7 +76,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
+          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
         </is>
       </c>
     </row>
@@ -88,7 +88,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:16:52</t>
+          <t xml:space="preserve">2026-08-27 01:26:17</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:13:39</t>
+          <t xml:space="preserve">2026-08-27 04:22:38</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">

--- a/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/06 · الموجة ج — المال.xlsx
@@ -76,7 +76,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
+          <t xml:space="preserve">05a0010b03fa63f30746693f8d0975301b1d7e49</t>
         </is>
       </c>
     </row>
@@ -88,7 +88,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:26:17</t>
+          <t xml:space="preserve">2026-08-27 01:31:07</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:22:38</t>
+          <t xml:space="preserve">2026-08-27 04:28:01</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
